--- a/kortdata/PU_markexpansion.xlsx
+++ b/kortdata/PU_markexpansion.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -468,6 +468,11 @@
           <t>Antal exemplar</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Form (rutor)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -487,6 +492,11 @@
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0]]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -506,6 +516,11 @@
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [2, 0]]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -525,6 +540,11 @@
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1]]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -544,6 +564,11 @@
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1], [1, 2]]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -563,6 +588,11 @@
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [2, 0]]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -582,6 +612,11 @@
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0]]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -601,6 +636,11 @@
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1]]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -620,6 +660,11 @@
       <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1]]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -639,6 +684,11 @@
       <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1]]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -658,6 +708,11 @@
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [1, 0]]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -677,6 +732,11 @@
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1]]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -696,6 +756,11 @@
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1]]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -715,6 +780,11 @@
       <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [2, 0]]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -734,6 +804,11 @@
       <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0]]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -753,6 +828,11 @@
       <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [1, 0]]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -771,6 +851,11 @@
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 1]]</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +1834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1887,6 +1972,28 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Antal tryckta kort per spel (utskrift_config: 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Form (rutor)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ej tryckt — markbitens form som [rad, kolumn] per ruta, avläst ur formbilden (Bilder/Former/Markexpansion_NN). Antal rutor = BYA / 250</t>
         </is>
       </c>
     </row>
